--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129056175</v>
       </c>
       <c r="B2" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129056174</v>
       </c>
       <c r="B3" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129056170</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129056175</v>
       </c>
       <c r="B2" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129056174</v>
       </c>
       <c r="B3" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129056170</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129056175</v>
       </c>
       <c r="B2" t="n">
-        <v>75159</v>
+        <v>75161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42613-2025 artfynd.xlsx
+++ b/artfynd/A 42613-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129056180</v>
       </c>
       <c r="B5" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
